--- a/1_mailing/2026_06_GBS_Lions_AI2/test.xlsx
+++ b/1_mailing/2026_06_GBS_Lions_AI2/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cyphral/Z_Dev/Adaptive_assistant/1_mailing/2026_06_GBS_Lions_AI2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6D8CF7-F863-6D47-A917-F88D9C0FF34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BC0252-79E9-1C4F-A571-14D521AADCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="680" windowWidth="28380" windowHeight="18440" xr2:uid="{1D968E92-3B61-9344-970E-C8763D7F311B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="recipients" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">recipients!$A$1:$D$884</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">recipients!$A$1:$D$877</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,14 +53,14 @@
     <t>robert.godziszewski@adaptivesag.com</t>
   </si>
   <si>
-    <t>INVITATION | Adaptive's GBS Lions' Talks in Katowice | AI as GBS Change Driver | 09.06.2026</t>
+    <t>AGENDA | Adaptive's GBS Lions' Talks in Katowice | AI as GBS Change Driver | 09.06.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -191,14 +191,6 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -501,7 +493,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -544,13 +536,11 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -584,7 +574,6 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -936,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB2A2FC-D8BF-4F42-A279-1028F28BF1F4}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.33203125" bestFit="1" customWidth="1"/>
@@ -967,12 +956,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D885" xr:uid="{1DB2A2FC-D8BF-4F42-A279-1028F28BF1F4}"/>
-  <conditionalFormatting sqref="A1002:A1036 A1064:A1048576 A3:A967 A1 A997:A1000">
+  <autoFilter ref="A1:D878" xr:uid="{1DB2A2FC-D8BF-4F42-A279-1028F28BF1F4}"/>
+  <conditionalFormatting sqref="A995:A1029 A1057:A1048576 A3:A960 A1 A990:A993">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
